--- a/benchmark/generated_files/RISP-1_M_025.xlsx
+++ b/benchmark/generated_files/RISP-1_M_025.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A2:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -443,31 +443,24 @@
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Banca: Conto Arancio</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IBAN: IT33 D034 4001 6000 0000 0468 012</t>
+          <t>Saldo iniziale: 19.781,43 EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saldo iniziale: 7.085,95 EUR</t>
+          <t>Banca: Conto Arancio</t>
         </is>
       </c>
     </row>
@@ -508,7 +501,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>475.53</v>
+        <v>598.5</v>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
@@ -527,7 +520,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>423.13</v>
+        <v>439.5</v>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="inlineStr">
@@ -546,7 +539,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>501.6</v>
+        <v>487.18</v>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="inlineStr">
@@ -565,7 +558,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>443.68</v>
+        <v>516.05</v>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
@@ -576,7 +569,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -584,7 +577,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>549.26</v>
+        <v>538.21</v>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="inlineStr">
@@ -595,7 +588,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -603,7 +596,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>448.27</v>
+        <v>560.11</v>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="inlineStr">
@@ -614,7 +607,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -622,7 +615,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>599.17</v>
+        <v>500.88</v>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="inlineStr">
@@ -633,7 +626,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -641,7 +634,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>425.6</v>
+        <v>482.91</v>
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="inlineStr">
@@ -652,7 +645,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -660,7 +653,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>415</v>
+        <v>472.65</v>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="inlineStr">
@@ -671,7 +664,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -679,7 +672,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>534.71</v>
+        <v>559.6900000000001</v>
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
@@ -690,7 +683,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -698,7 +691,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>407.16</v>
+        <v>487.49</v>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
@@ -709,7 +702,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -717,7 +710,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>583.49</v>
+        <v>425</v>
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="inlineStr">
@@ -728,7 +721,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46026</v>
+        <v>46029</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -736,7 +729,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>404.23</v>
+        <v>458.53</v>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="inlineStr">
@@ -747,7 +740,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -755,7 +748,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>543.36</v>
+        <v>582.24</v>
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="inlineStr">
@@ -766,7 +759,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -774,7 +767,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>584.4</v>
+        <v>593.37</v>
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="inlineStr">
@@ -785,7 +778,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -793,7 +786,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>572.8</v>
+        <v>423.85</v>
       </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="inlineStr">
@@ -804,7 +797,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -812,7 +805,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>555.4299999999999</v>
+        <v>468.52</v>
       </c>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="inlineStr">
@@ -823,7 +816,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -831,7 +824,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>496.15</v>
+        <v>468.56</v>
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
@@ -842,7 +835,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -850,7 +843,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>560.4299999999999</v>
+        <v>499.46</v>
       </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="inlineStr">
@@ -861,7 +854,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -869,7 +862,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>557.49</v>
+        <v>529.13</v>
       </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="inlineStr">
@@ -880,7 +873,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46030</v>
+        <v>46032</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -888,7 +881,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>596.29</v>
+        <v>472.12</v>
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="inlineStr">
@@ -899,7 +892,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46030</v>
+        <v>46032</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -907,7 +900,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>560.1900000000001</v>
+        <v>454.35</v>
       </c>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="inlineStr">
@@ -918,7 +911,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46030</v>
+        <v>46032</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -926,7 +919,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>518.9299999999999</v>
+        <v>544.83</v>
       </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="inlineStr">
@@ -937,17 +930,17 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n">
-        <v>27.7</v>
-      </c>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>590.49</v>
+      </c>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -956,7 +949,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -964,7 +957,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>436.26</v>
+        <v>518.77</v>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
@@ -975,7 +968,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -983,7 +976,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>443</v>
+        <v>420.63</v>
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
@@ -994,7 +987,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -1002,7 +995,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>552.9400000000001</v>
+        <v>411.55</v>
       </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="inlineStr">
@@ -1021,7 +1014,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>597.4</v>
+        <v>408.42</v>
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="inlineStr">
@@ -1032,7 +1025,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -1040,7 +1033,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>568.4</v>
+        <v>437.33</v>
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="inlineStr">
@@ -1059,7 +1052,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>479.95</v>
+        <v>423.16</v>
       </c>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="inlineStr">
@@ -1070,17 +1063,17 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>405.8</v>
-      </c>
-      <c r="D37" s="3" t="n"/>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>33.85</v>
+      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1089,7 +1082,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -1097,7 +1090,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>522.87</v>
+        <v>410.72</v>
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="inlineStr">
@@ -1108,7 +1101,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -1116,7 +1109,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>584.98</v>
+        <v>573.5599999999999</v>
       </c>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="inlineStr">
@@ -1127,7 +1120,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -1135,7 +1128,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>584.91</v>
+        <v>414.85</v>
       </c>
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="inlineStr">
@@ -1146,7 +1139,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -1154,7 +1147,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>599.17</v>
+        <v>534.83</v>
       </c>
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="inlineStr">
@@ -1165,7 +1158,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -1173,7 +1166,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>519.03</v>
+        <v>600</v>
       </c>
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="inlineStr">
@@ -1184,7 +1177,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46036</v>
+        <v>46039</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1192,7 +1185,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>417.86</v>
+        <v>542.51</v>
       </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="inlineStr">
@@ -1203,7 +1196,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1204,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>452.81</v>
+        <v>492.19</v>
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="inlineStr">
@@ -1222,7 +1215,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -1230,7 +1223,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>591.99</v>
+        <v>519.6799999999999</v>
       </c>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="inlineStr">
@@ -1241,7 +1234,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -1249,7 +1242,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>591.88</v>
+        <v>563.0599999999999</v>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="inlineStr">
@@ -1260,7 +1253,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46038</v>
+        <v>46040</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -1268,7 +1261,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>560.95</v>
+        <v>560.4400000000001</v>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="inlineStr">
@@ -1279,7 +1272,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -1287,7 +1280,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>441.12</v>
+        <v>567.0599999999999</v>
       </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="inlineStr">
@@ -1298,7 +1291,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1299,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>523.6900000000001</v>
+        <v>568.83</v>
       </c>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="inlineStr">
@@ -1317,7 +1310,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -1325,7 +1318,7 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>442.99</v>
+        <v>550.25</v>
       </c>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="inlineStr">
@@ -1336,7 +1329,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46039</v>
+        <v>46042</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -1344,7 +1337,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>492.49</v>
+        <v>471.67</v>
       </c>
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="inlineStr">
@@ -1355,7 +1348,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46039</v>
+        <v>46043</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -1363,7 +1356,7 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>577.75</v>
+        <v>426.65</v>
       </c>
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="inlineStr">
@@ -1374,7 +1367,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46040</v>
+        <v>46044</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -1382,7 +1375,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>572.75</v>
+        <v>576.71</v>
       </c>
       <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="inlineStr">
@@ -1393,7 +1386,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46040</v>
+        <v>46044</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -1401,7 +1394,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>505.62</v>
+        <v>434.52</v>
       </c>
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="inlineStr">
@@ -1412,7 +1405,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>441.35</v>
+        <v>515.12</v>
       </c>
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="inlineStr">
@@ -1431,7 +1424,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -1439,7 +1432,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>541.35</v>
+        <v>477.07</v>
       </c>
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="inlineStr">
@@ -1450,7 +1443,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46042</v>
+        <v>46047</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -1458,7 +1451,7 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>541.5700000000001</v>
+        <v>421.24</v>
       </c>
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="inlineStr">
@@ -1469,17 +1462,17 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>472.86</v>
-      </c>
-      <c r="D58" s="3" t="n"/>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>47.55</v>
+      </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1488,7 +1481,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -1496,7 +1489,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>461.56</v>
+        <v>547.53</v>
       </c>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="inlineStr">
@@ -1507,7 +1500,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1508,7 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>468.53</v>
+        <v>444.63</v>
       </c>
       <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="inlineStr">
@@ -1526,17 +1519,17 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>518.38</v>
-      </c>
-      <c r="D61" s="3" t="n"/>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>50.04</v>
+      </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1545,17 +1538,17 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n">
-        <v>22.59</v>
-      </c>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>571.23</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1564,7 +1557,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -1572,7 +1565,7 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>446.08</v>
+        <v>439.68</v>
       </c>
       <c r="D63" s="3" t="n"/>
       <c r="E63" s="3" t="inlineStr">
@@ -1583,7 +1576,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -1591,7 +1584,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>518.35</v>
+        <v>450.99</v>
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="inlineStr">
@@ -1602,7 +1595,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -1610,7 +1603,7 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>568.39</v>
+        <v>580.9400000000001</v>
       </c>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="inlineStr">
@@ -1621,17 +1614,17 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46046</v>
+        <v>46051</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n">
-        <v>47.76</v>
-      </c>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>499.68</v>
+      </c>
+      <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1640,7 +1633,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46046</v>
+        <v>46051</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -1648,7 +1641,7 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>523.61</v>
+        <v>518.6799999999999</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="inlineStr">
@@ -1659,7 +1652,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46046</v>
+        <v>46052</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -1667,7 +1660,7 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>591.99</v>
+        <v>411.3</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="inlineStr">
@@ -1678,17 +1671,17 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46047</v>
+        <v>46052</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n">
-        <v>24.79</v>
-      </c>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>481.97</v>
+      </c>
+      <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1697,7 +1690,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46047</v>
+        <v>46052</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -1705,7 +1698,7 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>522.62</v>
+        <v>487.98</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="3" t="inlineStr">
@@ -1716,7 +1709,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46047</v>
+        <v>46053</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -1724,7 +1717,7 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>563.85</v>
+        <v>522.9</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="inlineStr">
@@ -1735,7 +1728,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46048</v>
+        <v>46053</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -1743,7 +1736,7 @@
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>482.23</v>
+        <v>514.27</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="inlineStr">
@@ -1754,7 +1747,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1755,7 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>583.02</v>
+        <v>574.17</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="3" t="inlineStr">
@@ -1773,7 +1766,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -1781,7 +1774,7 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>502.99</v>
+        <v>558.99</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="inlineStr">
@@ -1792,7 +1785,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -1800,7 +1793,7 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>570.99</v>
+        <v>451.91</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="inlineStr">
@@ -1811,7 +1804,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -1819,7 +1812,7 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>444.74</v>
+        <v>507.25</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="inlineStr">
@@ -1830,7 +1823,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46050</v>
+        <v>46054</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1831,7 @@
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>412.09</v>
+        <v>446.11</v>
       </c>
       <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="inlineStr">
@@ -1849,7 +1842,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46050</v>
+        <v>46054</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -1857,7 +1850,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>568.95</v>
+        <v>520.03</v>
       </c>
       <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="inlineStr">
@@ -1868,7 +1861,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1869,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>502.46</v>
+        <v>518.77</v>
       </c>
       <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="inlineStr">
@@ -1887,7 +1880,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1888,7 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>560.65</v>
+        <v>531.84</v>
       </c>
       <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="inlineStr">
@@ -1906,7 +1899,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
@@ -1914,7 +1907,7 @@
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>494.77</v>
+        <v>523.79</v>
       </c>
       <c r="D81" s="3" t="n"/>
       <c r="E81" s="3" t="inlineStr">
@@ -1925,7 +1918,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
@@ -1933,7 +1926,7 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>411.07</v>
+        <v>583.8099999999999</v>
       </c>
       <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="inlineStr">
@@ -1944,7 +1937,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46053</v>
+        <v>46056</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
@@ -1952,7 +1945,7 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>552.51</v>
+        <v>523.35</v>
       </c>
       <c r="D83" s="3" t="n"/>
       <c r="E83" s="3" t="inlineStr">
@@ -1963,7 +1956,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46053</v>
+        <v>46056</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
@@ -1971,7 +1964,7 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>536.41</v>
+        <v>437.04</v>
       </c>
       <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="inlineStr">
@@ -1982,7 +1975,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46054</v>
+        <v>46056</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
@@ -1990,7 +1983,7 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>513.59</v>
+        <v>442.97</v>
       </c>
       <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="inlineStr">
@@ -2001,7 +1994,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2002,7 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>567.9299999999999</v>
+        <v>573.05</v>
       </c>
       <c r="D86" s="3" t="n"/>
       <c r="E86" s="3" t="inlineStr">
@@ -2020,7 +2013,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
@@ -2028,7 +2021,7 @@
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>587.03</v>
+        <v>539.4299999999999</v>
       </c>
       <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="inlineStr">
@@ -2039,7 +2032,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
@@ -2047,7 +2040,7 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>410.74</v>
+        <v>553.62</v>
       </c>
       <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="inlineStr">
@@ -2058,7 +2051,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2059,7 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>513.52</v>
+        <v>416.3</v>
       </c>
       <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="inlineStr">
@@ -2077,7 +2070,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2078,7 @@
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>597.26</v>
+        <v>425.09</v>
       </c>
       <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="inlineStr">
@@ -2096,7 +2089,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
@@ -2104,7 +2097,7 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>517.04</v>
+        <v>464.08</v>
       </c>
       <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="inlineStr">
@@ -2115,7 +2108,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
@@ -2123,7 +2116,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>530.88</v>
+        <v>479.27</v>
       </c>
       <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="inlineStr">
@@ -2134,17 +2127,17 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46056</v>
+        <v>46061</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>573.87</v>
-      </c>
-      <c r="D93" s="3" t="n"/>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>25.82</v>
+      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -2153,7 +2146,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46056</v>
+        <v>46061</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2154,7 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>556.35</v>
+        <v>451.02</v>
       </c>
       <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="inlineStr">
@@ -2172,7 +2165,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46056</v>
+        <v>46061</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
@@ -2180,7 +2173,7 @@
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>474.95</v>
+        <v>523.02</v>
       </c>
       <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="inlineStr">
@@ -2191,7 +2184,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
@@ -2199,7 +2192,7 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>597.71</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="D96" s="3" t="n"/>
       <c r="E96" s="3" t="inlineStr">
@@ -2210,7 +2203,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
@@ -2218,7 +2211,7 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>535.85</v>
+        <v>487.02</v>
       </c>
       <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="inlineStr">
@@ -2229,7 +2222,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2230,7 @@
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>558.37</v>
+        <v>462.68</v>
       </c>
       <c r="D98" s="3" t="n"/>
       <c r="E98" s="3" t="inlineStr">
@@ -2248,7 +2241,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
@@ -2256,7 +2249,7 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>499.83</v>
+        <v>496.68</v>
       </c>
       <c r="D99" s="3" t="n"/>
       <c r="E99" s="3" t="inlineStr">
@@ -2267,7 +2260,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
@@ -2275,7 +2268,7 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>425.48</v>
+        <v>590.12</v>
       </c>
       <c r="D100" s="3" t="n"/>
       <c r="E100" s="3" t="inlineStr">
@@ -2286,7 +2279,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
@@ -2294,7 +2287,7 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>545.59</v>
+        <v>506.68</v>
       </c>
       <c r="D101" s="3" t="n"/>
       <c r="E101" s="3" t="inlineStr">
@@ -2305,7 +2298,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2306,7 @@
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>571.74</v>
+        <v>444.19</v>
       </c>
       <c r="D102" s="3" t="n"/>
       <c r="E102" s="3" t="inlineStr">
@@ -2324,7 +2317,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
@@ -2332,7 +2325,7 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>454.18</v>
+        <v>408.48</v>
       </c>
       <c r="D103" s="3" t="n"/>
       <c r="E103" s="3" t="inlineStr">
@@ -2343,7 +2336,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
@@ -2351,7 +2344,7 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>447.83</v>
+        <v>430.44</v>
       </c>
       <c r="D104" s="3" t="n"/>
       <c r="E104" s="3" t="inlineStr">
@@ -2362,7 +2355,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
@@ -2370,7 +2363,7 @@
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>469.33</v>
+        <v>450.2</v>
       </c>
       <c r="D105" s="3" t="n"/>
       <c r="E105" s="3" t="inlineStr">
@@ -2381,7 +2374,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
@@ -2389,7 +2382,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>499.93</v>
+        <v>588.46</v>
       </c>
       <c r="D106" s="3" t="n"/>
       <c r="E106" s="3" t="inlineStr">
@@ -2400,7 +2393,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2401,7 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>424.84</v>
+        <v>502.82</v>
       </c>
       <c r="D107" s="3" t="n"/>
       <c r="E107" s="3" t="inlineStr">
@@ -2419,7 +2412,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
@@ -2427,7 +2420,7 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>546.73</v>
+        <v>406.63</v>
       </c>
       <c r="D108" s="3" t="n"/>
       <c r="E108" s="3" t="inlineStr">
@@ -2438,7 +2431,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
@@ -2446,7 +2439,7 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>477.42</v>
+        <v>410.6</v>
       </c>
       <c r="D109" s="3" t="n"/>
       <c r="E109" s="3" t="inlineStr">
@@ -2465,7 +2458,7 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>445.36</v>
+        <v>414.6</v>
       </c>
       <c r="D110" s="3" t="n"/>
       <c r="E110" s="3" t="inlineStr">
@@ -2484,7 +2477,7 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>569.9</v>
+        <v>417.96</v>
       </c>
       <c r="D111" s="3" t="n"/>
       <c r="E111" s="3" t="inlineStr">
@@ -2503,7 +2496,7 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>441.7</v>
+        <v>416.06</v>
       </c>
       <c r="D112" s="3" t="n"/>
       <c r="E112" s="3" t="inlineStr">
@@ -2514,7 +2507,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
@@ -2522,7 +2515,7 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>545.3200000000001</v>
+        <v>470.18</v>
       </c>
       <c r="D113" s="3" t="n"/>
       <c r="E113" s="3" t="inlineStr">
@@ -2533,7 +2526,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
@@ -2541,7 +2534,7 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>598.5700000000001</v>
+        <v>575.25</v>
       </c>
       <c r="D114" s="3" t="n"/>
       <c r="E114" s="3" t="inlineStr">
@@ -2552,7 +2545,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2553,7 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>562.28</v>
+        <v>525.85</v>
       </c>
       <c r="D115" s="3" t="n"/>
       <c r="E115" s="3" t="inlineStr">
@@ -2571,7 +2564,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
@@ -2579,7 +2572,7 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>573.6</v>
+        <v>400.25</v>
       </c>
       <c r="D116" s="3" t="n"/>
       <c r="E116" s="3" t="inlineStr">
@@ -2598,7 +2591,7 @@
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>519.74</v>
+        <v>550.24</v>
       </c>
       <c r="D117" s="3" t="n"/>
       <c r="E117" s="3" t="inlineStr">
@@ -2617,7 +2610,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>411.12</v>
+        <v>445.42</v>
       </c>
       <c r="D118" s="3" t="n"/>
       <c r="E118" s="3" t="inlineStr">
@@ -2636,7 +2629,7 @@
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>451.17</v>
+        <v>520.1</v>
       </c>
       <c r="D119" s="3" t="n"/>
       <c r="E119" s="3" t="inlineStr">
@@ -2655,7 +2648,7 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>528.77</v>
+        <v>419.17</v>
       </c>
       <c r="D120" s="3" t="n"/>
       <c r="E120" s="3" t="inlineStr">
@@ -2674,7 +2667,7 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>449.53</v>
+        <v>434</v>
       </c>
       <c r="D121" s="3" t="n"/>
       <c r="E121" s="3" t="inlineStr">
@@ -2685,7 +2678,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
@@ -2693,7 +2686,7 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>514.54</v>
+        <v>539.75</v>
       </c>
       <c r="D122" s="3" t="n"/>
       <c r="E122" s="3" t="inlineStr">
@@ -2712,7 +2705,7 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>485.6</v>
+        <v>478.12</v>
       </c>
       <c r="D123" s="3" t="n"/>
       <c r="E123" s="3" t="inlineStr">
@@ -2731,7 +2724,7 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>477.54</v>
+        <v>588</v>
       </c>
       <c r="D124" s="3" t="n"/>
       <c r="E124" s="3" t="inlineStr">
@@ -2742,7 +2735,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
@@ -2750,7 +2743,7 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>438.68</v>
+        <v>531.41</v>
       </c>
       <c r="D125" s="3" t="n"/>
       <c r="E125" s="3" t="inlineStr">
@@ -2761,7 +2754,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2762,7 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>586.66</v>
+        <v>553.28</v>
       </c>
       <c r="D126" s="3" t="n"/>
       <c r="E126" s="3" t="inlineStr">
@@ -2780,7 +2773,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
@@ -2788,7 +2781,7 @@
         </is>
       </c>
       <c r="C127" s="3" t="n">
-        <v>505</v>
+        <v>519.55</v>
       </c>
       <c r="D127" s="3" t="n"/>
       <c r="E127" s="3" t="inlineStr">
@@ -2799,7 +2792,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46073</v>
+        <v>46071</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
@@ -2807,7 +2800,7 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>443.97</v>
+        <v>510.12</v>
       </c>
       <c r="D128" s="3" t="n"/>
       <c r="E128" s="3" t="inlineStr">
@@ -2818,7 +2811,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46073</v>
+        <v>46071</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
@@ -2826,7 +2819,7 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>450.48</v>
+        <v>412.37</v>
       </c>
       <c r="D129" s="3" t="n"/>
       <c r="E129" s="3" t="inlineStr">
@@ -2837,7 +2830,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
@@ -2845,7 +2838,7 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>511.12</v>
+        <v>420.4</v>
       </c>
       <c r="D130" s="3" t="n"/>
       <c r="E130" s="3" t="inlineStr">
@@ -2856,7 +2849,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
@@ -2864,7 +2857,7 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>555.47</v>
+        <v>565.8200000000001</v>
       </c>
       <c r="D131" s="3" t="n"/>
       <c r="E131" s="3" t="inlineStr">
@@ -2875,7 +2868,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
@@ -2883,7 +2876,7 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>547.0700000000001</v>
+        <v>451.73</v>
       </c>
       <c r="D132" s="3" t="n"/>
       <c r="E132" s="3" t="inlineStr">
@@ -2894,7 +2887,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
@@ -2902,7 +2895,7 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>533.74</v>
+        <v>438.6</v>
       </c>
       <c r="D133" s="3" t="n"/>
       <c r="E133" s="3" t="inlineStr">
@@ -2913,7 +2906,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
@@ -2921,7 +2914,7 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>535.1900000000001</v>
+        <v>581.42</v>
       </c>
       <c r="D134" s="3" t="n"/>
       <c r="E134" s="3" t="inlineStr">
@@ -2932,7 +2925,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
@@ -2940,7 +2933,7 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>579.79</v>
+        <v>555.88</v>
       </c>
       <c r="D135" s="3" t="n"/>
       <c r="E135" s="3" t="inlineStr">
@@ -2951,7 +2944,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
@@ -2959,7 +2952,7 @@
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>580.6900000000001</v>
+        <v>512.39</v>
       </c>
       <c r="D136" s="3" t="n"/>
       <c r="E136" s="3" t="inlineStr">
@@ -2970,7 +2963,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
@@ -2978,7 +2971,7 @@
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>423.82</v>
+        <v>484.51</v>
       </c>
       <c r="D137" s="3" t="n"/>
       <c r="E137" s="3" t="inlineStr">
@@ -2989,7 +2982,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
@@ -2997,7 +2990,7 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>470.52</v>
+        <v>401.38</v>
       </c>
       <c r="D138" s="3" t="n"/>
       <c r="E138" s="3" t="inlineStr">
@@ -3008,7 +3001,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3009,7 @@
         </is>
       </c>
       <c r="C139" s="3" t="n">
-        <v>517.38</v>
+        <v>495.6</v>
       </c>
       <c r="D139" s="3" t="n"/>
       <c r="E139" s="3" t="inlineStr">
@@ -3027,7 +3020,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3028,7 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>473.03</v>
+        <v>489.4</v>
       </c>
       <c r="D140" s="3" t="n"/>
       <c r="E140" s="3" t="inlineStr">
@@ -3046,7 +3039,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3047,7 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>410.21</v>
+        <v>438.77</v>
       </c>
       <c r="D141" s="3" t="n"/>
       <c r="E141" s="3" t="inlineStr">
@@ -3065,7 +3058,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
@@ -3073,7 +3066,7 @@
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>528.34</v>
+        <v>482.67</v>
       </c>
       <c r="D142" s="3" t="n"/>
       <c r="E142" s="3" t="inlineStr">
@@ -3084,7 +3077,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
@@ -3092,7 +3085,7 @@
         </is>
       </c>
       <c r="C143" s="3" t="n">
-        <v>480.18</v>
+        <v>511.89</v>
       </c>
       <c r="D143" s="3" t="n"/>
       <c r="E143" s="3" t="inlineStr">
@@ -3103,7 +3096,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
@@ -3111,7 +3104,7 @@
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>442.88</v>
+        <v>531.6900000000001</v>
       </c>
       <c r="D144" s="3" t="n"/>
       <c r="E144" s="3" t="inlineStr">
@@ -3122,7 +3115,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
@@ -3130,7 +3123,7 @@
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>524.09</v>
+        <v>442.58</v>
       </c>
       <c r="D145" s="3" t="n"/>
       <c r="E145" s="3" t="inlineStr">
@@ -3141,7 +3134,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
@@ -3149,7 +3142,7 @@
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>572.71</v>
+        <v>413.72</v>
       </c>
       <c r="D146" s="3" t="n"/>
       <c r="E146" s="3" t="inlineStr">
@@ -3168,7 +3161,7 @@
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>497.86</v>
+        <v>458.99</v>
       </c>
       <c r="D147" s="3" t="n"/>
       <c r="E147" s="3" t="inlineStr">
@@ -3187,7 +3180,7 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>459.46</v>
+        <v>510.63</v>
       </c>
       <c r="D148" s="3" t="n"/>
       <c r="E148" s="3" t="inlineStr">
@@ -3206,7 +3199,7 @@
         </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>488.69</v>
+        <v>525.09</v>
       </c>
       <c r="D149" s="3" t="n"/>
       <c r="E149" s="3" t="inlineStr">
@@ -3218,7 +3211,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Saldo finale: 25.707,56 EUR</t>
+          <t>Saldo finale: 2.074,48 EUR</t>
         </is>
       </c>
     </row>
